--- a/artfynd/A 14313-2026 artfynd.xlsx
+++ b/artfynd/A 14313-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130962489</v>
+        <v>130962488</v>
       </c>
       <c r="B2" t="n">
-        <v>93138</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562929</v>
+        <v>562816</v>
       </c>
       <c r="R2" t="n">
-        <v>6730863</v>
+        <v>6730936</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130962547</v>
+        <v>130962489</v>
       </c>
       <c r="B3" t="n">
-        <v>93138</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562998</v>
+        <v>562929</v>
       </c>
       <c r="R3" t="n">
-        <v>6730827</v>
+        <v>6730863</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
+          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130962545</v>
+        <v>130962547</v>
       </c>
       <c r="B4" t="n">
-        <v>97883</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562758</v>
+        <v>562998</v>
       </c>
       <c r="R4" t="n">
-        <v>6730867</v>
+        <v>6730827</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130962490</v>
+        <v>130962544</v>
       </c>
       <c r="B5" t="n">
-        <v>97883</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563091</v>
+        <v>562760</v>
       </c>
       <c r="R5" t="n">
-        <v>6730737</v>
+        <v>6730841</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130962544</v>
+        <v>130962546</v>
       </c>
       <c r="B6" t="n">
-        <v>79002</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562760</v>
+        <v>562916</v>
       </c>
       <c r="R6" t="n">
-        <v>6730841</v>
+        <v>6730909</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130962488</v>
+        <v>130962487</v>
       </c>
       <c r="B7" t="n">
-        <v>93138</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562816</v>
+        <v>562773</v>
       </c>
       <c r="R7" t="n">
-        <v>6730936</v>
+        <v>6730843</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Inventering åt Structor Miljöpartner. Sparsamma förekommster</t>
+          <t>Inventering åt Structor Miljöpartner. Måttliga förekomster</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130962495</v>
+        <v>130962490</v>
       </c>
       <c r="B8" t="n">
-        <v>97883</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562985</v>
+        <v>563091</v>
       </c>
       <c r="R8" t="n">
-        <v>6730597</v>
+        <v>6730737</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130962487</v>
+        <v>130962495</v>
       </c>
       <c r="B9" t="n">
-        <v>97883</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562773</v>
+        <v>562985</v>
       </c>
       <c r="R9" t="n">
-        <v>6730843</v>
+        <v>6730597</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130962546</v>
+        <v>130962545</v>
       </c>
       <c r="B10" t="n">
-        <v>98935</v>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562916</v>
+        <v>562758</v>
       </c>
       <c r="R10" t="n">
-        <v>6730909</v>
+        <v>6730867</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 14313-2026 artfynd.xlsx
+++ b/artfynd/A 14313-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962489</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962547</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962490</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962495</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,8 +1635,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>